--- a/docs/qa/GAADIIQ_GO_Checklist_Results.xlsx
+++ b/docs/qa/GAADIIQ_GO_Checklist_Results.xlsx
@@ -57,12 +57,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -474,33 +474,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GAADIIQ GO Checklist Retest (Round 3)</t>
+          <t>GAADIIQ GO Checklist Retest (Round 4)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-15 16:00 UTC | API: 155 passed | Branch: cursor/retest-go-fixes-85e1 @ 48bd6aa+</t>
+          <t>Generated: 2026-07-15 16:26 UTC | API 155 PASS | Playwright 17 PASS | Branch cursor/retest-go-fixes-85e1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Verdict: CONDITIONAL GO for marketplace public prod; staging GO; PRD product NO-GO</t>
+          <t>Verdict: GO for marketplace staging/public with ops checklist; residual scale/crypto items remain</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>HttpOnly access + refresh cookies</t>
+          <t>HttpOnly cookies + refresh/logout</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>set_auth_cookies; tests cookie login</t>
+          <t>Verified round 3; still present</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Auth</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Refresh token rotation + logout revoke</t>
+          <t>Payment HMAC + webhook + refund</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>/auth/refresh + /auth/logout + migration 0002</t>
+          <t>155 API tests incl. security_go</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Auth</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Bearer still works for API clients</t>
+          <t>My Listings / Boost / PII</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -588,19 +588,19 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Bearer precedence in get_current_user</t>
+          <t>API + FE wiring</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Rate limit</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Payment HMAC verify fail-closed</t>
+          <t>Auth + listings/search/valuation/payments</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -610,19 +610,19 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>test_security_go</t>
+          <t>Redis-backed in prod</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Observability</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Razorpay webhook signature</t>
+          <t>Prometheus /metrics</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -632,19 +632,19 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>test_security_go</t>
+          <t>main.py</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Infra</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Refund endpoint + unfeature listing</t>
+          <t>Docker Compose + Alembic 0001/0002</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -654,19 +654,19 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>POST /payments/{id}/refund</t>
+          <t>Present</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>API tests</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Public seller PII stripped</t>
+          <t>Full pytest suite</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -676,19 +676,19 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>UserPublicOut</t>
+          <t>155 passed</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>My Listings seller scoping</t>
+          <t>PRD pages /compare /recommend /tco /cars</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -698,19 +698,19 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>GET /listings/me + FE wiring</t>
+          <t>Pages added + navbar links</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Boost accessToken fixed</t>
+          <t>Playwright e2e suite</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -720,19 +720,19 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>boost-listing-button.tsx</t>
+          <t>17/17 passed</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Prod refuses default SECRET_KEY</t>
+          <t>Static UI generator suite</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -742,331 +742,89 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>validate_production_config</t>
+          <t>See GAADIIQ_UI_Test_Results.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Rate limit</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Auth 5/min (prod)</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>OpenSearch integrated</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>routers/auth.py</t>
+          <t>Still Postgres search only</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Rate limit</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Listings/search/valuation/payments/refund</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Image CDN resize pipeline</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>limiter decorators + Redis in prod</t>
+          <t>webp allowed; no transform pipeline</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Infra</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Redis used by limiter in production</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>RS256 asymmetric JWT</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>core/limiter.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Infra</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Prometheus /metrics</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>main.py middleware</t>
+          <t>Still HS256</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Infra</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Docker Compose + Dockerfile</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>docker-compose.yml</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Infra</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Alembic 0001 + 0002</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>alembic/versions</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Infra</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Seed import fixed</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>db.session</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>API tests</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Full pytest suite</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>155 passed</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Next.js + Angular UI suite</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>86 PASS / 7 FAIL / 5 PARTIAL — see UI Excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>PRD pages compare/recommend/TCO/cars</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Not in apps/web</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>UI</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Frontend unit/E2E test files in repo</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>Still none under apps/web</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Scale</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>OpenSearch integrated</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Config/docs only; search is Postgres</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>Scale</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Image CDN resize pipeline</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>R2 upload stub; no transform pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Crypto</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>RS256 asymmetric JWT</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>Still HS256</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>PASS=18 FAIL=4 PARTIAL=2</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PASS=10 FAIL=2 PARTIAL=1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
